--- a/Dataset/IT/xlsx/ITAMed_2019.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2019.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Immunologia e Reumatologia; Anestesia e Rianimazione</t>
+          <t>Immunologia e Reumatologia</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Medicina Legale</t>
+          <t>Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Anestesia e Rianimazione</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Neurologia e Neurochirurgia; Anestesia e Rianimazione</t>
+          <t>Neurologia e Neurochirurgia</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Anestesia e Rianimazione; Chirurgia Generale</t>
+          <t>Anestesia e Rianimazione</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1468,7 +1468,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Chirurgia Generale</t>
+          <t>Chirurgia Generale; Malattie Infettive</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Diagnostica per Immagini e Medicina Nucleare; Oncologia</t>
+          <t>Diagnostica per Immagini e Medicina Nucleare</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Oncologia; Gastroenterologia</t>
+          <t>Gastroenterologia; Oncologia</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1990,7 +1990,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Dermatologia e Venereologia; Chirurgia Generale</t>
+          <t>Chirurgia Generale</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Endocrinologia; Farmacologia e Tossicologia</t>
+          <t>Endocrinologia</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica; Genetica Medica</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Cardiologia e Cardiochirurgia</t>
+          <t>Cardiologia e Cardiochirurgia; Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Pneumologia e Chirurgia Toracica</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Ginecologia e Ostetricia; Ematologia</t>
+          <t>Ginecologia e Ostetricia</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Gastroenterologia; Ematologia</t>
+          <t>Gastroenterologia</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Pneumologia e Chirurgia Toracica</t>
+          <t>Malattie Infettive; Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>Ematologia; Ginecologia e Ostetricia</t>
+          <t>Ginecologia e Ostetricia; Ematologia</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Malattie Infettive</t>
+          <t>Malattie Infettive; Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -6196,7 +6196,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Malattie Infettive; Neurologia e Neurochirurgia</t>
+          <t>Neurologia e Neurochirurgia; Malattie Infettive</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Pediatria; Psichiatria</t>
+          <t>Pediatria</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Oncologia; Pneumologia e Chirurgia Toracica</t>
+          <t>Pneumologia e Chirurgia Toracica</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Pediatria</t>
+          <t>Pediatria; Otorinolaringoiatria</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>Otorinolaringoiatria; Pediatria</t>
+          <t>Pediatria; Otorinolaringoiatria</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -7308,7 +7308,7 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>Cardiologia e Cardiochirurgia; Pediatria</t>
+          <t>Pediatria; Cardiologia e Cardiochirurgia</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -7482,7 +7482,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Genetica Medica; Pediatria</t>
+          <t>Pediatria; Genetica Medica</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>Nefrologia; Pediatria</t>
+          <t>Pediatria; Nefrologia</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -7598,7 +7598,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>Ematologia; Pediatria</t>
+          <t>Genetica Medica</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>Endocrinologia; Pediatria</t>
+          <t>Pediatria; Endocrinologia</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Farmacologia e Tossicologia; Igiene, Epidemiologia e Statistica</t>
+          <t>Farmacologia e Tossicologia</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">

--- a/Dataset/IT/xlsx/ITAMed_2019.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2019.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Immagine</t>
+          <t>question_type</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -603,7 +603,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -719,7 +719,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -777,7 +777,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -835,7 +835,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -893,7 +893,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -951,7 +951,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1241,7 +1241,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1647,7 +1647,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1705,7 +1705,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1821,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1879,7 +1879,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1937,7 +1937,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2111,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2169,7 +2169,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2411,7 +2411,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2469,7 +2469,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2643,7 +2643,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2701,7 +2701,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2759,7 +2759,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2875,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -2991,7 +2991,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3223,7 +3223,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3397,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3455,7 +3455,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3571,7 +3571,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3687,7 +3687,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -3977,7 +3977,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4335,7 +4335,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4451,7 +4451,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4509,7 +4509,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4567,7 +4567,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4741,7 +4741,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -4973,7 +4973,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5147,7 +5147,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5205,7 +5205,7 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5263,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5379,7 +5379,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5495,7 +5495,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6017,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -6085,7 +6085,7 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6259,7 +6259,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6375,7 +6375,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6433,7 +6433,7 @@
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6607,7 +6607,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6723,7 +6723,7 @@
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6781,7 +6781,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -6839,7 +6839,7 @@
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -6897,7 +6897,7 @@
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>case-based</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7255,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7429,7 +7429,7 @@
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7545,7 +7545,7 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7835,7 +7835,7 @@
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -7951,7 +7951,7 @@
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>knowledge-based</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -8019,7 +8019,7 @@
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8077,7 +8077,7 @@
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="L133" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8251,7 +8251,7 @@
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8309,7 +8309,7 @@
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8367,7 +8367,7 @@
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8425,7 +8425,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>knowledge-based</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8599,7 @@
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>case-based</t>
         </is>
       </c>
     </row>

--- a/Dataset/IT/xlsx/ITAMed_2019.xlsx
+++ b/Dataset/IT/xlsx/ITAMed_2019.xlsx
@@ -412,7 +412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N141"/>
+  <dimension ref="A1:O141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="14.20703125" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -477,15 +477,20 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>question_type</t>
+          <t>Tipo Domanda</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
+          <t>Immagine</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>Categoria Immagine</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Percorso Immagine</t>
         </is>
@@ -548,6 +553,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -606,6 +616,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -664,6 +679,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -722,6 +742,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -780,6 +805,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -838,6 +868,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -896,6 +931,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -954,6 +994,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1012,6 +1057,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1070,6 +1120,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1128,6 +1183,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1186,6 +1246,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1244,6 +1309,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1302,6 +1372,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1360,6 +1435,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1418,6 +1498,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1476,6 +1561,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1534,6 +1624,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1592,6 +1687,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1650,6 +1750,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1708,6 +1813,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1766,6 +1876,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1824,6 +1939,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1882,6 +2002,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1940,6 +2065,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1998,6 +2128,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2056,6 +2191,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2114,6 +2254,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2172,6 +2317,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2230,6 +2380,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2290,10 +2445,15 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
           <t>Photograph of a skin lesion</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>images/2019/ssm201960.png</t>
         </is>
@@ -2356,6 +2516,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2414,6 +2579,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2472,6 +2642,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -2530,6 +2705,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -2588,6 +2768,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -2646,6 +2831,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -2704,6 +2894,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -2762,6 +2957,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2820,6 +3020,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -2878,6 +3083,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2936,6 +3146,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2994,6 +3209,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3052,6 +3272,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3110,6 +3335,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3168,6 +3398,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3226,6 +3461,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3284,6 +3524,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3342,6 +3587,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -3400,6 +3650,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -3458,6 +3713,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -3516,6 +3776,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -3574,6 +3839,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -3632,6 +3902,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -3690,6 +3965,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -3748,6 +4028,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -3806,6 +4091,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -3864,6 +4154,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -3922,6 +4217,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -3982,10 +4282,15 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
           <t>Chest X-ray</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>images/2019/ssm2019119.png</t>
         </is>
@@ -4048,6 +4353,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4106,6 +4416,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4164,6 +4479,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4222,6 +4542,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -4280,6 +4605,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -4338,6 +4668,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -4396,6 +4731,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -4454,6 +4794,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -4512,6 +4857,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -4570,6 +4920,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -4628,6 +4983,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -4686,6 +5046,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -4744,6 +5109,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -4802,6 +5172,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -4860,6 +5235,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -4918,6 +5298,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -4976,6 +5361,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5034,6 +5424,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5092,6 +5487,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -5150,6 +5550,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -5208,6 +5613,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -5266,6 +5676,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -5324,6 +5739,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -5382,6 +5802,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -5440,6 +5865,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -5498,6 +5928,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -5556,6 +5991,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -5614,6 +6054,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -5672,6 +6117,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -5730,6 +6180,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -5788,6 +6243,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5846,6 +6306,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -5904,6 +6369,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5962,6 +6432,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -6022,10 +6497,15 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr">
+      <c r="O96" t="inlineStr">
         <is>
           <t>images/2019/ssm2019189.png</t>
         </is>
@@ -6088,6 +6568,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -6146,6 +6631,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -6204,6 +6694,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -6262,6 +6757,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -6320,6 +6820,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -6378,6 +6883,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6436,6 +6946,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -6494,6 +7009,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -6552,6 +7072,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -6610,6 +7135,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -6668,6 +7198,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -6726,6 +7261,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6784,6 +7324,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -6842,6 +7387,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6902,10 +7452,15 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
           <t>Upper limb X-ray</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr">
+      <c r="O111" t="inlineStr">
         <is>
           <t>images/2019/ssm2019216.png</t>
         </is>
@@ -6968,6 +7523,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -7026,6 +7586,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -7084,6 +7649,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -7142,6 +7712,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -7200,6 +7775,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -7258,6 +7838,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -7316,6 +7901,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -7374,6 +7964,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -7432,6 +8027,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -7490,6 +8090,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -7545,7 +8150,12 @@
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7606,6 +8216,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -7664,6 +8279,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7722,6 +8342,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7777,7 +8402,12 @@
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>case-based</t>
+          <t>knowledge-based</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -7838,6 +8468,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7896,6 +8531,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -7956,10 +8596,15 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
           <t>Brain CT scan</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr">
+      <c r="O129" t="inlineStr">
         <is>
           <t>images/2019/ssm2019254.png</t>
         </is>
@@ -8022,6 +8667,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -8080,6 +8730,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -8138,6 +8793,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -8196,6 +8856,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -8254,6 +8919,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -8312,6 +8982,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -8370,6 +9045,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -8428,6 +9108,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -8486,6 +9171,11 @@
           <t>knowledge-based</t>
         </is>
       </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -8544,6 +9234,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -8602,6 +9297,11 @@
           <t>case-based</t>
         </is>
       </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -8658,6 +9358,11 @@
       <c r="L141" t="inlineStr">
         <is>
           <t>case-based</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
     </row>
